--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260511_211207.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
